--- a/scripts/assets/yandex-business/price-list.xlsx
+++ b/scripts/assets/yandex-business/price-list.xlsx
@@ -497,14 +497,10 @@
           <t>https://proverkastaza.ru/tarify/</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
+      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>Да</t>
         </is>
       </c>
     </row>
@@ -542,14 +538,10 @@
           <t>https://proverkastaza.ru/tarify/</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
+      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>Да</t>
         </is>
       </c>
     </row>
@@ -587,14 +579,10 @@
           <t>https://proverkastaza.ru/proverka-stazha/</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
+      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>Да</t>
         </is>
       </c>
     </row>

--- a/scripts/assets/yandex-business/price-list.xlsx
+++ b/scripts/assets/yandex-business/price-list.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -522,7 +522,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Подготовка документов, черновики заявлений и контроль этапов до обращения. Без обещания перерасчёта или конкретной суммы выплат. Решение по существу принимает СФР.</t>
+          <t>Подготовка документов, проект обращения и контроль этапов до обращения. Без обещания перерасчёта или конкретной суммы выплат. Решение по существу принимает СФР.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -563,7 +563,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Диагностика плюс сопровождение по документам и этапам до подачи в СФР. Фиксированная цена по соглашению. Сервис не заменяет СФР и не гарантирует перерасчёт.</t>
+          <t>Диагностика плюс сопровождение по документам и этапам до подачи в СФР. Фиксированная цена по соглашению. Перенос трудовой в Word при заказе — 100 ₽ за разворот. Сервис не заменяет СФР и не гарантирует перерасчёт.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -585,6 +585,43 @@
           <t>Да</t>
         </is>
       </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Проверка стажа</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Перенос трудовой в таблицу Word (за разворот)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>trudovaya-word-100</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Перенос видимых записей из бумажной трудовой книжки в таблицу Word для сверки. Цена за 1 разворот; итог — по числу разворотов после сканов в кабинете. Не является решением СФР и не гарантирует перерасчёт.</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Таблица Word по трудовой. 100 ₽ за разворот.</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>100</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>https://proverkastaza.ru/tarify/</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/scripts/assets/yandex-business/price-list.xlsx
+++ b/scripts/assets/yandex-business/price-list.xlsx
@@ -604,12 +604,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Перенос видимых записей из бумажной трудовой книжки в таблицу Word для сверки. Цена за 1 разворот; итог — по числу разворотов после сканов в кабинете. Не является решением СФР и не гарантирует перерасчёт.</t>
+          <t>Перенос видимых записей из бумажной трудовой в таблицу Word. 100 ₽ за 1 разворот. Тяжёлый объём — отдельный счёт после осмотра сканов в кабинете. Не является решением СФР и не гарантирует перерасчёт.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Таблица Word по трудовой. 100 ₽ за разворот.</t>
+          <t>Таблица Word. 100 ₽/разворот; тяжёлый — отдельный счёт.</t>
         </is>
       </c>
       <c r="F5" t="n">

--- a/scripts/assets/yandex-business/price-list.xlsx
+++ b/scripts/assets/yandex-business/price-list.xlsx
@@ -471,22 +471,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Диагностика проверки стажа</t>
+          <t>Шаг 1. Диагностика проверки стажа</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>diag-3000</t>
+          <t>step1-diag-3000</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Проверка документов и выписки ИЛС. Первичный план действий и индивидуальный чек-лист. Сервис не является СФР: решение о перерасчёте принимает Социальный фонд России. Условия закрепляются в соглашении.</t>
+          <t>Проверка документов и выписки ИЛС; первичный план и чек-лист. Оплата поэтапная — следующий шаг только если нужен. Сервис не является СФР: решение о перерасчёте принимает Социальный фонд России. Условия закрепляются в соглашении.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Проверка документов и план действий. Без гарантии перерасчёта.</t>
+          <t>Диагностика и план. Поэтапная оплата. Без гарантии перерасчёта.</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -512,26 +512,26 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Сопровождение по документам и этапам</t>
+          <t>Шаг 2. Подготовка документов</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>support-10000</t>
+          <t>step2-docs-5000</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Подготовка документов, проект обращения и контроль этапов до обращения. Без обещания перерасчёта или конкретной суммы выплат. Решение по существу принимает СФР.</t>
+          <t>Сборка комплекта под ситуацию, черновики запросов и пояснений, список чего добрать. Оплачивается отдельно после диагностики. Без обещания перерасчёта. Решение принимает СФР.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Подготовка документов и контроль этапов до обращения в СФР.</t>
+          <t>Подготовка документов. Отдельный шаг после диагностики.</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>10000</v>
+        <v>5000</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -553,30 +553,30 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Комплекс Под ключ: диагностика и сопровождение</t>
+          <t>Шаг 3. Сопровождение до подачи</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>turnkey-25000</t>
+          <t>step3-support-8000</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Диагностика плюс сопровождение по документам и этапам до подачи в СФР. Фиксированная цена по соглашению. Перенос трудовой в Word при заказе — 100 ₽ за разворот. Сервис не заменяет СФР и не гарантирует перерасчёт.</t>
+          <t>Проект обращения, пошаговый план и подсказки по подаче через СФР, МФЦ или Госуслуги; контроль известных сроков до вашей подачи. Оплачивается отдельно. Сервис не заменяет СФР и не гарантирует перерасчёт.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Диагностика и сопровождение до подачи. Фиксированная цена.</t>
+          <t>Сопровождение до вашей подачи. Отдельный шаг.</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>25000</v>
+        <v>8000</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://proverkastaza.ru/proverka-stazha/</t>
+          <t>https://proverkastaza.ru/tarify/</t>
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
